--- a/UK_CoP_TitleLists/BMJ_Open_scifreeimport.xlsx
+++ b/UK_CoP_TitleLists/BMJ_Open_scifreeimport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d4b02a2393526de/Documents/CoP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{8E33EB6E-B497-4DAB-9947-1B04FC7367F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6569BF34-E6CF-4B12-8F61-3622D0E9A17D}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{8E33EB6E-B497-4DAB-9947-1B04FC7367F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D655DCFC-58C6-4EF8-BB2C-84E38909B40D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BE44926E-75A4-4EDC-A463-0127E7F3749D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="172">
   <si>
     <t>Journal Title</t>
   </si>
@@ -548,6 +548,12 @@
   </si>
   <si>
     <t>1756-1833</t>
+  </si>
+  <si>
+    <t>CC BY, CC-BY-NC</t>
+  </si>
+  <si>
+    <t>Note: Updated licences to include CC-BY-NC where applicable</t>
   </si>
 </sst>
 </file>
@@ -758,7 +764,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -821,10 +827,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -836,9 +839,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -846,6 +846,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1910,6 +1913,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2333,39 +2340,39 @@
       <c r="D2" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="31" t="s">
         <v>154</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H2" s="20"/>
       <c r="J2"/>
     </row>
     <row r="3" spans="1:11" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="28" t="s">
         <v>145</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="28"/>
       <c r="D3" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="30" t="s">
         <v>153</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="29"/>
+        <v>170</v>
+      </c>
+      <c r="H3" s="28"/>
       <c r="J3"/>
     </row>
     <row r="4" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -2379,39 +2386,39 @@
       <c r="D4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="31" t="s">
         <v>152</v>
       </c>
       <c r="F4" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H4" s="20"/>
       <c r="J4"/>
     </row>
     <row r="5" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>149</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="28"/>
       <c r="D5" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="30" t="s">
         <v>151</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="29"/>
+        <v>170</v>
+      </c>
+      <c r="H5" s="28"/>
       <c r="J5"/>
     </row>
     <row r="6" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -2425,39 +2432,39 @@
       <c r="D6" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="31" t="s">
         <v>108</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H6" s="20"/>
       <c r="J6"/>
     </row>
     <row r="7" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>157</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="28"/>
       <c r="D7" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="31" t="s">
         <v>155</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="29"/>
+        <v>170</v>
+      </c>
+      <c r="H7" s="28"/>
       <c r="J7"/>
     </row>
     <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -2471,7 +2478,7 @@
       <c r="D8" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="31" t="s">
         <v>109</v>
       </c>
       <c r="F8" s="20" t="s">
@@ -2501,7 +2508,7 @@
         <v>35</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H9" s="20"/>
     </row>
@@ -2523,7 +2530,7 @@
         <v>35</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H10" s="20"/>
       <c r="J10"/>
@@ -2540,14 +2547,14 @@
       <c r="D11" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="31" t="s">
         <v>112</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H11" s="20"/>
       <c r="J11"/>
@@ -2570,7 +2577,7 @@
         <v>35</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H12" s="20"/>
       <c r="J12"/>
@@ -2586,14 +2593,14 @@
       <c r="D13" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="31" t="s">
         <v>114</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H13" s="20"/>
       <c r="J13"/>
@@ -2616,7 +2623,7 @@
         <v>35</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H14" s="20"/>
       <c r="J14"/>
@@ -2639,7 +2646,7 @@
         <v>35</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H15" s="20"/>
       <c r="J15"/>
@@ -2662,7 +2669,7 @@
         <v>35</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H16" s="20"/>
       <c r="J16"/>
@@ -2678,14 +2685,14 @@
       <c r="D17" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="31" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H17" s="20"/>
       <c r="J17"/>
@@ -2701,14 +2708,14 @@
       <c r="D18" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="31" t="s">
         <v>119</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H18" s="20"/>
       <c r="J18"/>
@@ -2731,7 +2738,7 @@
         <v>35</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H19" s="20"/>
       <c r="J19"/>
@@ -2747,14 +2754,14 @@
       <c r="D20" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="31" t="s">
         <v>121</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H20" s="20"/>
       <c r="J20"/>
@@ -2777,7 +2784,7 @@
         <v>35</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H21" s="20"/>
       <c r="J21"/>
@@ -2793,14 +2800,14 @@
       <c r="D22" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="31" t="s">
         <v>123</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H22" s="20"/>
       <c r="J22"/>
@@ -2823,7 +2830,7 @@
         <v>35</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H23" s="20"/>
       <c r="J23"/>
@@ -2839,14 +2846,14 @@
       <c r="D24" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="31" t="s">
         <v>125</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H24" s="20"/>
       <c r="J24"/>
@@ -2862,14 +2869,14 @@
       <c r="D25" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="31" t="s">
         <v>127</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H25" s="20"/>
       <c r="J25"/>
@@ -2885,14 +2892,14 @@
       <c r="D26" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="31" t="s">
         <v>128</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H26" s="20"/>
       <c r="J26"/>
@@ -2908,39 +2915,39 @@
       <c r="D27" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="31" t="s">
         <v>130</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H27" s="20"/>
       <c r="J27"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>164</v>
       </c>
       <c r="B28" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="29"/>
+      <c r="C28" s="28"/>
       <c r="D28" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="31" t="s">
         <v>165</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H28" s="29"/>
+        <v>170</v>
+      </c>
+      <c r="H28" s="28"/>
       <c r="J28"/>
     </row>
     <row r="29" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -2954,14 +2961,14 @@
       <c r="D29" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H29" s="20"/>
       <c r="J29"/>
@@ -2977,14 +2984,14 @@
       <c r="D30" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="31" t="s">
         <v>132</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H30" s="20"/>
       <c r="J30"/>
@@ -3000,14 +3007,14 @@
       <c r="D31" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="31" t="s">
         <v>133</v>
       </c>
       <c r="F31" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H31" s="20"/>
       <c r="J31"/>
@@ -3023,14 +3030,14 @@
       <c r="D32" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="31" t="s">
         <v>134</v>
       </c>
       <c r="F32" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H32" s="20"/>
       <c r="J32"/>
@@ -3046,14 +3053,14 @@
       <c r="D33" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="31" t="s">
         <v>135</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H33" s="20"/>
       <c r="J33"/>
@@ -3069,39 +3076,39 @@
       <c r="D34" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="31" t="s">
         <v>136</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H34" s="20"/>
       <c r="J34"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="28" t="s">
         <v>167</v>
       </c>
       <c r="B35" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="36" t="s">
+      <c r="C35" s="28"/>
+      <c r="D35" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="31" t="s">
         <v>168</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H35" s="29"/>
+        <v>170</v>
+      </c>
+      <c r="H35" s="28"/>
       <c r="J35"/>
     </row>
     <row r="36" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -3115,39 +3122,39 @@
       <c r="D36" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="31" t="s">
         <v>137</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="H36" s="20"/>
       <c r="J36"/>
     </row>
     <row r="37" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30" t="s">
+      <c r="C37" s="29"/>
+      <c r="D37" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="30" t="s">
+      <c r="E37" s="29" t="s">
         <v>138</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="G37" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H37" s="30"/>
+      <c r="G37" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H37" s="29"/>
       <c r="J37"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
@@ -7517,11 +7524,14 @@
     <hyperlink ref="E5" r:id="rId32" xr:uid="{A911B494-7E0E-4131-9A63-600EA8BD5D96}"/>
     <hyperlink ref="E3" r:id="rId33" xr:uid="{A784C18E-BD6A-4AA5-8379-83BF11BF1B07}"/>
     <hyperlink ref="D35" r:id="rId34" display="https://www.worldcat.org/search?fq=x0:jrnl&amp;q=n2:1756-1833" xr:uid="{61546E4A-3FCB-47B9-92AE-CE86D67D13F1}"/>
+    <hyperlink ref="E7" r:id="rId35" xr:uid="{23B173A0-2BAF-48D9-958A-63B508ACB8E9}"/>
+    <hyperlink ref="E28" r:id="rId36" xr:uid="{7BE63728-929B-40C0-B545-12FF7AF00708}"/>
+    <hyperlink ref="E35" r:id="rId37" xr:uid="{85660DDA-DA17-4558-A7AB-C7AAEC2EFFC2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId35"/>
+  <pageSetup orientation="portrait" r:id="rId38"/>
   <tableParts count="1">
-    <tablePart r:id="rId36"/>
+    <tablePart r:id="rId39"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7545,30 +7555,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
     </row>
     <row r="4" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
@@ -7625,59 +7635,59 @@
         <v>36</v>
       </c>
       <c r="H5" s="22"/>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="33" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="29"/>
+      <c r="H6" s="28"/>
       <c r="I6" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="28"/>
+      <c r="D7" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="29"/>
+      <c r="H7" s="28"/>
       <c r="I7" s="9" t="s">
         <v>160</v>
       </c>
@@ -7686,82 +7696,82 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="29"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="9" t="s">
         <v>150</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="29"/>
+      <c r="H8" s="28"/>
       <c r="I8" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33" t="s">
+      <c r="C9" s="28"/>
+      <c r="D9" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="33"/>
+      <c r="H9" s="28"/>
       <c r="I9" s="9" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="29"/>
-      <c r="I10" s="34" t="s">
+      <c r="H10" s="28"/>
+      <c r="I10" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="33" t="s">
         <v>162</v>
       </c>
     </row>
@@ -7832,7 +7842,9 @@
       <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
+      <c r="A14" s="9" t="s">
+        <v>171</v>
+      </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
